--- a/Assignment 1 - Test cases.xlsx
+++ b/Assignment 1 - Test cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\ITPM_Assignment_1_Final\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7E4583A-AFC7-4C80-8151-EC56BBC276BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC44F482-896C-41AD-9165-A6FDAA5D835F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="722" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="286">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -52,13 +52,13 @@
     <t>S</t>
   </si>
   <si>
-    <t>mta clz1k thynw.</t>
-  </si>
-  <si>
-    <t>මට classඑකක් තියෙනවා.</t>
-  </si>
-  <si>
-    <t>mට clz1ක් thynw.</t>
+    <t>wifi eka wada na.</t>
+  </si>
+  <si>
+    <t>wifi එක වැඩ නෑ.</t>
+  </si>
+  <si>
+    <t>wඉfඉ එක wඅඩ න.</t>
   </si>
   <si>
     <t>FAIL</t>
@@ -67,773 +67,835 @@
     <t>English Digital Terms in Singlish</t>
   </si>
   <si>
-    <t>Evidence: "clz1k" Rationale: Uses abbreviation for class</t>
+    <t>Evidence: "wifi" Rationale: Uses the digital term Wi-Fi.</t>
   </si>
   <si>
     <t>Neg_0002</t>
   </si>
   <si>
-    <t>mn ada ynw.</t>
-  </si>
-  <si>
-    <t>මන් අද යනවා.</t>
-  </si>
-  <si>
-    <t>ම්න් අද yන්w.</t>
+    <t>router eka off karanna.</t>
+  </si>
+  <si>
+    <t>router එක off කරන්න.</t>
+  </si>
+  <si>
+    <t>රොඋටෙර් එක ඔෆ්ෆ් කරන්න.</t>
+  </si>
+  <si>
+    <t>Evidence: "router" Rationale: Uses the digital hardware term router.</t>
+  </si>
+  <si>
+    <t>Neg_0003</t>
+  </si>
+  <si>
+    <t>mthk krnn epa.</t>
+  </si>
+  <si>
+    <t>මතක් කරන්න එපා.</t>
+  </si>
+  <si>
+    <t>mථ්k kර්න්න් එපා.</t>
   </si>
   <si>
     <t>Vowel Omission in Singlish Words</t>
   </si>
   <si>
-    <t>Evidence: "mn ada ynw" Rationale: Vowels omitted from man and yanawa</t>
-  </si>
-  <si>
-    <t>Neg_0003</t>
-  </si>
-  <si>
-    <t>krnn dheyak na.</t>
-  </si>
-  <si>
-    <t>කරන්න දෙයක් නෑ.</t>
-  </si>
-  <si>
-    <t>kර්න්න් දෙයක් නෑ.</t>
-  </si>
-  <si>
-    <t>Evidence: "krnn" Rationale: Vowels omitted from karanna</t>
+    <t>Evidence: "mthk krnn" Rationale: Vowels omitted from mathak and karanna.</t>
   </si>
   <si>
     <t>Neg_0004</t>
   </si>
   <si>
-    <t>Fcbk eke photo1k damma.</t>
-  </si>
-  <si>
-    <t>Facebook එකේ photoඑකක් දැම්මා.</t>
-  </si>
-  <si>
-    <t>Fcbk එකේ photo1ක් දැම්මා.</t>
+    <t>pldhnn kiyanna.</t>
+  </si>
+  <si>
+    <t>පළඳින්න කියන්න.</t>
+  </si>
+  <si>
+    <t>pල්ධ්න්න් කියන්න.</t>
+  </si>
+  <si>
+    <t>Evidence: "pldhnn" Rationale: Vowels omitted from paladhinna.</t>
+  </si>
+  <si>
+    <t>Neg_0005</t>
+  </si>
+  <si>
+    <t>insta eke dmma.</t>
+  </si>
+  <si>
+    <t>Instagram එකේ දැම්මා.</t>
+  </si>
+  <si>
+    <t>ඉන්ස්ට එකෙ dම්ම.</t>
   </si>
   <si>
     <t>Platform/App Names in Singlish</t>
   </si>
   <si>
-    <t>Evidence: "Fcbk" Rationale: Abbreviated app name Facebook</t>
-  </si>
-  <si>
-    <t>Neg_0005</t>
-  </si>
-  <si>
-    <t>wtsapp eken call1k ganna.</t>
-  </si>
-  <si>
-    <t>whatsapp එකෙන් callඑකක් ගන්න.</t>
-  </si>
-  <si>
-    <t>wට්සප් එකෙන් call1ක් ගන්න.</t>
-  </si>
-  <si>
-    <t>Evidence: "wtsapp" Rationale: Abbreviated app name WhatsApp</t>
+    <t>Evidence: "insta" Rationale: Abbreviated app name for Instagram.</t>
   </si>
   <si>
     <t>Neg_0006</t>
   </si>
   <si>
+    <t>tiktok eka blnna.</t>
+  </si>
+  <si>
+    <t>TikTok එක බලන්න.</t>
+  </si>
+  <si>
+    <t>ටික්ටොක් එක bල්න්න.</t>
+  </si>
+  <si>
+    <t>Evidence: "tiktok" Rationale: App name TikTok is used.</t>
+  </si>
+  <si>
+    <t>Neg_0007</t>
+  </si>
+  <si>
+    <t>ammbooo pattai eka.</t>
+  </si>
+  <si>
+    <t>අම්මෝ පට්ටයි ඒක.</t>
+  </si>
+  <si>
+    <t>අම්ම්බොඔඔ පට්ටය් එක.</t>
+  </si>
+  <si>
+    <t>Inputs with Slang and Casual Phrasing</t>
+  </si>
+  <si>
+    <t>Evidence: "ammbooo pattai" Rationale: Uses colloquial slang ammbooo and pattai.</t>
+  </si>
+  <si>
+    <t>Neg_0008</t>
+  </si>
+  <si>
+    <t>maru bhande meka.</t>
+  </si>
+  <si>
+    <t>මරු භාණ්ඩේ මේක.</t>
+  </si>
+  <si>
+    <t>මරු bහන්ඩෙ මෙක.</t>
+  </si>
+  <si>
+    <t>Evidence: "maru bhande" Rationale: Uses casual slang terms.</t>
+  </si>
+  <si>
+    <t>Neg_0009</t>
+  </si>
+  <si>
+    <t>ada paper eka amarui.</t>
+  </si>
+  <si>
+    <t>අද paper එක අමාරුයි.</t>
+  </si>
+  <si>
+    <t>අද පපෙර් එක අමාරුය්.</t>
+  </si>
+  <si>
+    <t>Isolated English Word Insertions in Singlish</t>
+  </si>
+  <si>
+    <t>Evidence: "paper" Rationale: English word inserted directly.</t>
+  </si>
+  <si>
+    <t>Neg_0010</t>
+  </si>
+  <si>
+    <t>car eka gennanna.</t>
+  </si>
+  <si>
+    <t>car එක ගෙන්නන්න.</t>
+  </si>
+  <si>
+    <t>චර් එක ගෙන්නන්න.</t>
+  </si>
+  <si>
+    <t>Evidence: "car" Rationale: English word car inserted.</t>
+  </si>
+  <si>
+    <t>Neg_0011</t>
+  </si>
+  <si>
+    <t>oyata salli onida?</t>
+  </si>
+  <si>
+    <t>ඔයාට සල්ලි ඕනිද?</t>
+  </si>
+  <si>
+    <t>ඔයාට සල්ලි ඔනිඩ?</t>
+  </si>
+  <si>
+    <t>Inputs with punctuation marks</t>
+  </si>
+  <si>
+    <t>Evidence: "onida?" Rationale: Ends with a standard question mark.</t>
+  </si>
+  <si>
+    <t>Neg_0012</t>
+  </si>
+  <si>
+    <t>eka hari, api yamu.</t>
+  </si>
+  <si>
+    <t>ඒක හරි, අපි යමු.</t>
+  </si>
+  <si>
+    <t>එක හරි, අපි යමු.</t>
+  </si>
+  <si>
+    <t>Evidence: "hari," Rationale: Uses a comma for pausing.</t>
+  </si>
+  <si>
+    <t>Neg_0013</t>
+  </si>
+  <si>
+    <t>mta2k dhenna.</t>
+  </si>
+  <si>
+    <t>මට දෙකක් දෙන්න.</t>
+  </si>
+  <si>
+    <t>mට2k ධෙන්න.</t>
+  </si>
+  <si>
+    <t>Numeric Replacement for Words</t>
+  </si>
+  <si>
+    <t>Evidence: "2k" Rationale: Number 2 replaces the word deka.</t>
+  </si>
+  <si>
+    <t>Neg_0014</t>
+  </si>
+  <si>
+    <t>eka3k thiyenawa.</t>
+  </si>
+  <si>
+    <t>ඒක තුනක් තියෙනවා.</t>
+  </si>
+  <si>
+    <t>එක3k තියෙනwඅ.</t>
+  </si>
+  <si>
+    <t>Evidence: "3k" Rationale: Number 3 replaces the word thuna.</t>
+  </si>
+  <si>
+    <t>Neg_0015</t>
+  </si>
+  <si>
+    <t>gedhara enawadha?</t>
+  </si>
+  <si>
+    <t>ගෙදර එනවද?</t>
+  </si>
+  <si>
+    <t>ගෙධර එනwඅධ?</t>
+  </si>
+  <si>
+    <t>Romanization/Spelling Variants</t>
+  </si>
+  <si>
+    <t>Evidence: "gedhara", "enawadha" Rationale: Uses 'dh' instead of 'd' as a spelling variant.</t>
+  </si>
+  <si>
+    <t>Neg_0016</t>
+  </si>
+  <si>
+    <t>kohomadh wada?</t>
+  </si>
+  <si>
+    <t>කොහොමද වැඩ?</t>
+  </si>
+  <si>
+    <t>කොහොමධ් wඅඩ?</t>
+  </si>
+  <si>
+    <t>Evidence: "kohomadh" Rationale: Uses 'dh' instead of 'da' at the end of the word.</t>
+  </si>
+  <si>
+    <t>Neg_0017</t>
+  </si>
+  <si>
+    <t>heta 8:45 AM enna.</t>
+  </si>
+  <si>
+    <t>හෙට 8:45 AM එන්න.</t>
+  </si>
+  <si>
+    <t>හෙට 8:45 aම් එන්න.</t>
+  </si>
+  <si>
+    <t>Inputs with Time Formats</t>
+  </si>
+  <si>
+    <t>Evidence: "8:45 AM" Rationale: Time format with AM included.</t>
+  </si>
+  <si>
+    <t>Neg_0018</t>
+  </si>
+  <si>
+    <t>19:30 ta patan gamu.</t>
+  </si>
+  <si>
+    <t>19:30 ට පටන් ගමු.</t>
+  </si>
+  <si>
+    <t>19:30 ට pඅටන් ගමු.</t>
+  </si>
+  <si>
+    <t>Evidence: "19:30" Rationale: 24-hour time format used.</t>
+  </si>
+  <si>
+    <t>Neg_0019</t>
+  </si>
+  <si>
     <t>M</t>
   </si>
   <si>
-    <t>plz mt hlp1k dnnko.</t>
-  </si>
-  <si>
-    <t>please මට helpඑකක් දෙන්නකෝ.</t>
-  </si>
-  <si>
-    <t>plz mt hlp1ක් dන්න්ko.</t>
-  </si>
-  <si>
-    <t>Inputs with Slang and Casual Phrasing</t>
-  </si>
-  <si>
-    <t>Evidence: "plz mt hlp1k" Rationale: Uses casual slang plz, hlp</t>
-  </si>
-  <si>
-    <t>Neg_0007</t>
-  </si>
-  <si>
-    <t>scl ekee wrk wadiy.</t>
-  </si>
-  <si>
-    <t>school එකේ වැඩ වැඩියි.</t>
-  </si>
-  <si>
-    <t>scl එකේ wර්ක් wඅඩිය්.</t>
-  </si>
-  <si>
-    <t>Isolated English Word Insertions in Singlish</t>
-  </si>
-  <si>
-    <t>Evidence: "scl" Rationale: Isolated English word school abbreviated</t>
-  </si>
-  <si>
-    <t>Neg_0008</t>
-  </si>
-  <si>
-    <t>100%k sure da?</t>
-  </si>
-  <si>
-    <t>100%ක් sure ද?</t>
-  </si>
-  <si>
-    <t>100%k sure ද?</t>
-  </si>
-  <si>
-    <t>Inputs with punctuation marks</t>
-  </si>
-  <si>
-    <t>Evidence: "100%k sure da?" Rationale: Uses percentage and question marks</t>
-  </si>
-  <si>
-    <t>Neg_0009</t>
-  </si>
-  <si>
-    <t>mchn mta 500k dpnko.</t>
-  </si>
-  <si>
-    <t>මචන් මට 500ක් දාපන්කෝ.</t>
-  </si>
-  <si>
-    <t>mච්න් mට 500k dප්න්ko.</t>
-  </si>
-  <si>
-    <t>Evidence: "mchn", "dpnko" Rationale: Uses slang words machan and dapan</t>
-  </si>
-  <si>
-    <t>Neg_0010</t>
-  </si>
-  <si>
-    <t>clz1t ymw.</t>
-  </si>
-  <si>
-    <t>classඑකට යමු.</t>
-  </si>
-  <si>
-    <t>clz1ට් ymw.</t>
-  </si>
-  <si>
-    <t>Numeric Replacement for Words</t>
-  </si>
-  <si>
-    <t>Evidence: "clz1t" Rationale: Uses 1 to replace eka</t>
-  </si>
-  <si>
-    <t>Neg_0011</t>
-  </si>
-  <si>
-    <t>MaTa OnI nAa.</t>
-  </si>
-  <si>
-    <t>මට ඕනි නෑ.</t>
-  </si>
-  <si>
-    <t>MඅTඅ Oන්I nAඅ.</t>
-  </si>
-  <si>
-    <t>Romanization/Spelling Variants</t>
-  </si>
-  <si>
-    <t>Evidence: "MaTa OnI nAa" Rationale: Mixed capitalization spelling variant</t>
-  </si>
-  <si>
-    <t>Neg_0012</t>
-  </si>
-  <si>
-    <t>GeDaRa YaMu.</t>
-  </si>
-  <si>
-    <t>ගෙදර යමු.</t>
-  </si>
-  <si>
-    <t>GඑDඅRඅ YඅMඋ.</t>
-  </si>
-  <si>
-    <t>Evidence: "GeDaRa YaMu" Rationale: Mixed capitalization spelling variant</t>
-  </si>
-  <si>
-    <t>Neg_0013</t>
-  </si>
-  <si>
-    <t>meeting1ta join wenna.</t>
-  </si>
-  <si>
-    <t>meetingඑකට join වෙන්න.</t>
-  </si>
-  <si>
-    <t>meeting1ට join wඑන්න.</t>
-  </si>
-  <si>
-    <t>Evidence: "meeting1ta" Rationale: Uses 1 to replace eka</t>
-  </si>
-  <si>
-    <t>Neg_0014</t>
-  </si>
-  <si>
-    <t>pdfeka ewanna.</t>
-  </si>
-  <si>
-    <t>pdfඑක එවන්න.</t>
-  </si>
-  <si>
-    <t>pdfඑක එwඅන්න.</t>
-  </si>
-  <si>
-    <t>Evidence: "pdfeka" Rationale: Uses English digital term pdf</t>
-  </si>
-  <si>
-    <t>Neg_0015</t>
-  </si>
-  <si>
-    <t>4pmta clz eka.</t>
-  </si>
-  <si>
-    <t>4pmට class එක.</t>
-  </si>
-  <si>
-    <t>4pmtඅ clz එක.</t>
-  </si>
-  <si>
-    <t>Inputs with Time Formats</t>
-  </si>
-  <si>
-    <t>Evidence: "4pmta" Rationale: Uses time format pm</t>
-  </si>
-  <si>
-    <t>Neg_0016</t>
-  </si>
-  <si>
-    <t>10:30am weddi enna.</t>
-  </si>
-  <si>
-    <t>10:30am වෙද්දී එන්න.</t>
-  </si>
-  <si>
-    <t>10:30am wඑද්දී එන්න.</t>
-  </si>
-  <si>
-    <t>Evidence: "10:30am" Rationale: Uses time format with am</t>
-  </si>
-  <si>
-    <t>Neg_0017</t>
-  </si>
-  <si>
-    <t>ado0oo patta seen1.</t>
-  </si>
-  <si>
-    <t>අඩෝඕඕ පට්ට seenඑක.</t>
-  </si>
-  <si>
-    <t>ado0oo පට්ට seen1.</t>
-  </si>
-  <si>
-    <t>Evidence: "ado0oo" Rationale: Uses 0 to elongate the vowel</t>
-  </si>
-  <si>
-    <t>Neg_0018</t>
-  </si>
-  <si>
-    <t>ennnnnna epaa.</t>
-  </si>
-  <si>
-    <t>එන්නන්නන්න එපා.</t>
-  </si>
-  <si>
-    <t>එන්න්න්න්න්න එපා.</t>
-  </si>
-  <si>
-    <t>Evidence: "ennnnnna" Rationale: Repetition of consonant n</t>
-  </si>
-  <si>
-    <t>Neg_0019</t>
-  </si>
-  <si>
-    <t>yammmu heta.</t>
-  </si>
-  <si>
-    <t>යම්ම්මු හෙට.</t>
-  </si>
-  <si>
-    <t>Evidence: "yammmu" Rationale: Repetition of consonant m</t>
+    <t>rs. 150.50 k dhenna.</t>
+  </si>
+  <si>
+    <t>රුපියල් 150.50 ක් දෙන්න.</t>
+  </si>
+  <si>
+    <t>ර්ස්. 150.50 k ධෙන්න.</t>
+  </si>
+  <si>
+    <t>Inputs with Currency and Pricing</t>
+  </si>
+  <si>
+    <t>Evidence: "rs. 150.50" Rationale: Uses currency abbreviation and decimal pricing.</t>
   </si>
   <si>
     <t>Neg_0020</t>
   </si>
   <si>
-    <t>rs.5000/= k denawada?</t>
-  </si>
-  <si>
-    <t>rs.5000/= ක් දෙනවද?</t>
-  </si>
-  <si>
-    <t>rs.5000/= k දෙනwඅඩ?</t>
-  </si>
-  <si>
-    <t>Evidence: "rs.5000/= k" Rationale: Uses multiple punctuation and math symbols</t>
+    <t>LKR 5000 /= gewanna.</t>
+  </si>
+  <si>
+    <t>රුපියල් 5000/= ගෙවන්න.</t>
+  </si>
+  <si>
+    <t>ල්ක්ර් 5000 /= ගෙwඅන්න.</t>
+  </si>
+  <si>
+    <t>Evidence: "LKR 5000 /=" Rationale: Uses LKR prefix and /= suffix.</t>
   </si>
   <si>
     <t>Neg_0021</t>
   </si>
   <si>
-    <t>eka100%k aththa.</t>
-  </si>
-  <si>
-    <t>ඒක100%ක් ඇත්ත.</t>
-  </si>
-  <si>
-    <t>එක100%k ඇත්ත.</t>
-  </si>
-  <si>
-    <t>Evidence: "100%k" Rationale: Uses percentage symbol</t>
+    <t>https://lms.sliit.lk ekata yamu.</t>
+  </si>
+  <si>
+    <t>https://lms.sliit.lk එකට යමු.</t>
+  </si>
+  <si>
+    <t>හ්ට්ට්ප්ස්://ල්ම්ස්.ස්ලීට්.ල්ක් එකට යමු.</t>
+  </si>
+  <si>
+    <t>Inputs with URLs and Web Addresses</t>
+  </si>
+  <si>
+    <t>Evidence: "https://lms.sliit.lk" Rationale: Contains a full web address.</t>
   </si>
   <si>
     <t>Neg_0022</t>
   </si>
   <si>
-    <t>www.sliit.lk ekata yanna.</t>
-  </si>
-  <si>
-    <t>www.sliit.lk එකට යන්න.</t>
-  </si>
-  <si>
-    <t>wව්ව්.sliit.lක් එකට යන්න.</t>
-  </si>
-  <si>
-    <t>Evidence: "www.sliit.lk" Rationale: Uses a URL web address</t>
+    <t>google.com eke balanna.</t>
+  </si>
+  <si>
+    <t>google.com එකේ බලන්න.</t>
+  </si>
+  <si>
+    <t>ගොඔග්ලෙ.චොම් එකෙ බලන්න.</t>
+  </si>
+  <si>
+    <t>Evidence: "google.com" Rationale: Contains a standard domain name.</t>
   </si>
   <si>
     <t>Neg_0023</t>
   </si>
   <si>
-    <t>test@gmail.com ta ewanna.</t>
-  </si>
-  <si>
-    <t>test@gmail.com ට එවන්න.</t>
-  </si>
-  <si>
-    <t>test@gmail.coම් ට එwඅන්න.</t>
-  </si>
-  <si>
-    <t>Evidence: "test@gmail.com" Rationale: Uses an email address</t>
+    <t>admin@sliit.lk ta mail ekak.</t>
+  </si>
+  <si>
+    <t>admin@sliit.lk ට mail එකක්.</t>
+  </si>
+  <si>
+    <t>අඩ්මින්@ස්ලීට්.ල්ක් ට මඉල් එකක්.</t>
+  </si>
+  <si>
+    <t>Inputs with Email Addresses</t>
+  </si>
+  <si>
+    <t>Evidence: "admin@sliit.lk" Rationale: Uses a complete email address format.</t>
   </si>
   <si>
     <t>Neg_0024</t>
   </si>
   <si>
-    <t>2024di api meet wemu.</t>
-  </si>
-  <si>
-    <t>2024දී අපි meet වෙමු.</t>
-  </si>
-  <si>
-    <t>2024dඉ අපි meet wඑමු.</t>
-  </si>
-  <si>
-    <t>Evidence: "2024di" Rationale: Number attached directly to a suffix</t>
+    <t>info@company.com baluwada?</t>
+  </si>
+  <si>
+    <t>info@company.com බැලුවද?</t>
+  </si>
+  <si>
+    <t>ඉන්ෆො@චොම්පන්ය්.චොම් bඅලුwඅඩ?</t>
+  </si>
+  <si>
+    <t>Evidence: "info@company.com" Rationale: Uses a standard email address format.</t>
   </si>
   <si>
     <t>Neg_0025</t>
   </si>
   <si>
-    <t>5kgk gennanna.</t>
-  </si>
-  <si>
-    <t>5kgක් ගෙන්නන්න.</t>
-  </si>
-  <si>
-    <t>5kග්k ගෙන්නන්න.</t>
-  </si>
-  <si>
-    <t>Evidence: "5kgk" Rationale: Number and measurement mixed with suffix</t>
+    <t>2025/12/01 weddi iwarai.</t>
+  </si>
+  <si>
+    <t>2025/12/01 වෙද්දී ඉවරයි.</t>
+  </si>
+  <si>
+    <t>2025/12/01 wඑද්දී ඉwඅරය්.</t>
+  </si>
+  <si>
+    <t>Inputs with Date and Year Formats</t>
+  </si>
+  <si>
+    <t>Evidence: "2025/12/01" Rationale: Uses a YYYY/MM/DD date format.</t>
   </si>
   <si>
     <t>Neg_0026</t>
   </si>
   <si>
-    <t>phn1 charge na.</t>
-  </si>
-  <si>
-    <t>phoneඑක charge නෑ.</t>
-  </si>
-  <si>
-    <t>phn1 charge න.</t>
-  </si>
-  <si>
-    <t>Evidence: "phn1" Rationale: Abbreviated digital term phone with 1</t>
+    <t>15-Aug-2024 dhi gamu.</t>
+  </si>
+  <si>
+    <t>15-Aug-2024 දී ගමු.</t>
+  </si>
+  <si>
+    <t>15-අඋග්-2024 ධි ගමු.</t>
+  </si>
+  <si>
+    <t>Evidence: "15-Aug-2024" Rationale: Uses date format with month abbreviation.</t>
   </si>
   <si>
     <t>Neg_0027</t>
   </si>
   <si>
-    <t>ekayi2yi3yi</t>
-  </si>
-  <si>
-    <t>එකයි2යි3යි</t>
-  </si>
-  <si>
-    <t>eකය්i2yඉ3yඉ</t>
-  </si>
-  <si>
-    <t>Evidence: "ekayi2yi3yi" Rationale: Multiple numbers merged with suffixes</t>
+    <t>150km k yanna oni.</t>
+  </si>
+  <si>
+    <t>150km ක් යන්න ඕනි.</t>
+  </si>
+  <si>
+    <t>150ක්ම් k යන්න ඔනි.</t>
+  </si>
+  <si>
+    <t>Inputs with Measurement Units</t>
+  </si>
+  <si>
+    <t>Evidence: "150km" Rationale: Contains the measurement unit km for kilometers.</t>
   </si>
   <si>
     <t>Neg_0028</t>
   </si>
   <si>
-    <t>mekaeka wage.</t>
-  </si>
-  <si>
-    <t>මේකඑක වගේ.</t>
-  </si>
-  <si>
-    <t>මෙකෙක wඅගෙ.</t>
-  </si>
-  <si>
-    <t>Evidence: "mekaeka" Rationale: Two words typed continuously without space</t>
+    <t>250g k gennanna.</t>
+  </si>
+  <si>
+    <t>250g ක් ගෙන්නන්න.</t>
+  </si>
+  <si>
+    <t>250ග් k ගෙන්නන්න.</t>
+  </si>
+  <si>
+    <t>Evidence: "250g" Rationale: Contains the measurement unit g for grams.</t>
   </si>
   <si>
     <t>Neg_0029</t>
   </si>
   <si>
-    <t>apiyamu gedara.</t>
-  </si>
-  <si>
-    <t>අපියමු ගෙදර.</t>
-  </si>
-  <si>
-    <t>අපියමු ගෙඩර.</t>
-  </si>
-  <si>
-    <t>Evidence: "apiyamu" Rationale: Two words typed continuously without space</t>
+    <t>oyataadareykutiyenawa.</t>
+  </si>
+  <si>
+    <t>ඔයාට ආදරයෙකුත් තියෙනවා.</t>
+  </si>
+  <si>
+    <t>ඔයාටඅඩරෙය්කුටියෙනwඅ.</t>
+  </si>
+  <si>
+    <t>Missing Spaces / Joined Words</t>
+  </si>
+  <si>
+    <t>Evidence: "oyataadareykutiyenawa" Rationale: Multiple words joined without standard spaces.</t>
   </si>
   <si>
     <t>Neg_0030</t>
   </si>
   <si>
-    <t>mekakiyawanna balanna.</t>
-  </si>
-  <si>
-    <t>මේකකියවන්න බලන්න.</t>
-  </si>
-  <si>
-    <t>මෙකකියwඅන්න බලන්න.</t>
-  </si>
-  <si>
-    <t>Evidence: "mekakiyawanna" Rationale: Multiple words joined without space</t>
+    <t>mataepawela thiyenne.</t>
+  </si>
+  <si>
+    <t>මට එපා වෙලා තියෙන්නේ.</t>
+  </si>
+  <si>
+    <t>මටඑපwඑල තියෙන්නෙ.</t>
+  </si>
+  <si>
+    <t>Evidence: "mataepawela" Rationale: Two words joined as one.</t>
   </si>
   <si>
     <t>Neg_0031</t>
   </si>
   <si>
-    <t>kmmly mata.</t>
-  </si>
-  <si>
-    <t>කම්මැලියි මට.</t>
-  </si>
-  <si>
-    <t>kම්ම්ly මට.</t>
-  </si>
-  <si>
-    <t>Evidence: "kmmly" Rationale: Casual abbreviation of kammali</t>
+    <t>ai mehema karanne?</t>
+  </si>
+  <si>
+    <t>ඇයි මෙහෙම කරන්නේ?</t>
+  </si>
+  <si>
+    <t>අය් මෙහෙම කරන්නෙ?</t>
+  </si>
+  <si>
+    <t>Question forms</t>
+  </si>
+  <si>
+    <t>Evidence: "ai mehema karanne?" Rationale: Interrogative sentence structure asking why.</t>
   </si>
   <si>
     <t>Neg_0032</t>
   </si>
   <si>
-    <t>sxt wenawa eka.</t>
-  </si>
-  <si>
-    <t>set වෙනවා ඒක.</t>
-  </si>
-  <si>
-    <t>sxt wඑනwඅ එක.</t>
-  </si>
-  <si>
-    <t>Evidence: "sxt" Rationale: Typing variant x used instead of e</t>
+    <t>koheda oya inne?</t>
+  </si>
+  <si>
+    <t>කොහෙද ඔයා ඉන්නේ?</t>
+  </si>
+  <si>
+    <t>කොහෙඩ ඔයා ඉන්නෙ?</t>
+  </si>
+  <si>
+    <t>Evidence: "koheda oya inne?" Rationale: Interrogative sentence asking where.</t>
   </si>
   <si>
     <t>Neg_0033</t>
   </si>
   <si>
-    <t>msg1k danna.</t>
-  </si>
-  <si>
-    <t>msgඑකක් දාන්න.</t>
-  </si>
-  <si>
-    <t>msg1ක් ඩාන්න.</t>
-  </si>
-  <si>
-    <t>Evidence: "msg1k" Rationale: Digital term msg combined with 1k</t>
+    <t>laptopeken wada karanna.</t>
+  </si>
+  <si>
+    <t>laptop එකෙන් වැඩ කරන්න.</t>
+  </si>
+  <si>
+    <t>ලප්ටොපෙකෙන් wඅඩ කරන්න.</t>
+  </si>
+  <si>
+    <t>English Words with Singlish Suffixes</t>
+  </si>
+  <si>
+    <t>Evidence: "laptopeken" Rationale: English word laptop joined with Singlish suffix eken.</t>
   </si>
   <si>
     <t>Neg_0034</t>
   </si>
   <si>
-    <t>asgmt eka dunna.</t>
-  </si>
-  <si>
-    <t>assignment එක දුන්නා.</t>
-  </si>
-  <si>
-    <t>asgmt එක ඩුන්න.</t>
-  </si>
-  <si>
-    <t>Evidence: "asgmt" Rationale: Abbreviation of English word assignment</t>
+    <t>busakata naginna.</t>
+  </si>
+  <si>
+    <t>bus එකකට නගින්න.</t>
+  </si>
+  <si>
+    <t>බුසකට නගින්න.</t>
+  </si>
+  <si>
+    <t>Evidence: "busakata" Rationale: English word bus joined with suffix akata.</t>
   </si>
   <si>
     <t>Neg_0035</t>
   </si>
   <si>
-    <t>mge nama kamal.</t>
-  </si>
-  <si>
-    <t>මගේ නම කමල්.</t>
-  </si>
-  <si>
-    <t>ම්ගෙ නම කමල්.</t>
-  </si>
-  <si>
-    <t>Evidence: "mge" Rationale: Spelling variant dropping first vowel</t>
+    <t>monawada me???</t>
+  </si>
+  <si>
+    <t>මොනවද මේ???</t>
+  </si>
+  <si>
+    <t>මොනwඅඩ මෙ???</t>
+  </si>
+  <si>
+    <t>Inputs with Multiple Punctuation Marks</t>
+  </si>
+  <si>
+    <t>Evidence: "???" Rationale: Three question marks used consecutively.</t>
   </si>
   <si>
     <t>Neg_0036</t>
   </si>
   <si>
-    <t>kyyda ganana?</t>
-  </si>
-  <si>
-    <t>කීයද ගණන?</t>
-  </si>
-  <si>
-    <t>kය්ය්dඅ ගනන?</t>
-  </si>
-  <si>
-    <t>Question forms</t>
-  </si>
-  <si>
-    <t>Evidence: "kyyda ganana?" Rationale: Question phrase with double y spelling</t>
+    <t>pissu hadenawa!!!</t>
+  </si>
+  <si>
+    <t>පිස්සු හැදෙනවා!!!</t>
+  </si>
+  <si>
+    <t>පිස්සු හඩෙනwඅ!!!</t>
+  </si>
+  <si>
+    <t>Evidence: "!!!" Rationale: Three exclamation marks used consecutively.</t>
   </si>
   <si>
     <t>Neg_0037</t>
   </si>
   <si>
-    <t>krnn epa.</t>
-  </si>
-  <si>
-    <t>කරන්න එපා.</t>
-  </si>
-  <si>
-    <t>kර්න්න් එපා.</t>
-  </si>
-  <si>
-    <t>Evidence: "krnn epa." Rationale: Complete omission of vowels</t>
+    <t>balamu ithin...</t>
+  </si>
+  <si>
+    <t>බලමු ඉතින්...</t>
+  </si>
+  <si>
+    <t>bඅලමු ඉතින්...</t>
+  </si>
+  <si>
+    <t>Inputs with Trailing Punctuation / Ellipses</t>
+  </si>
+  <si>
+    <t>Evidence: "ithin..." Rationale: Uses an ellipsis at the end of the phrase.</t>
   </si>
   <si>
     <t>Neg_0038</t>
   </si>
   <si>
-    <t>blnn puluwanda.</t>
-  </si>
-  <si>
-    <t>බලන්න පුළුවන්ද.</t>
-  </si>
-  <si>
-    <t>bල්න්න් පුලුwඅන්ඩ.</t>
-  </si>
-  <si>
-    <t>Evidence: "blnn puluwanda." Rationale: Question with omitted vowels in balanna</t>
+    <t>hari balannam..</t>
+  </si>
+  <si>
+    <t>හරි බලන්නම්..</t>
+  </si>
+  <si>
+    <t>හරි bඅලන්නම්..</t>
+  </si>
+  <si>
+    <t>Evidence: "balannam.." Rationale: Uses trailing dots indicating a pause or unfinished thought.</t>
   </si>
   <si>
     <t>Neg_0039</t>
   </si>
   <si>
-    <t>officeekata yamu.</t>
-  </si>
-  <si>
-    <t>officeඑකට යමු.</t>
-  </si>
-  <si>
-    <t>Evidence: "officeekata" Rationale: English word office directly attached to suffix</t>
+    <t>niiiyamai eka.</t>
+  </si>
+  <si>
+    <t>නියමයි ඒක.</t>
+  </si>
+  <si>
+    <t>නිය්ය්ය්මයි එක.</t>
+  </si>
+  <si>
+    <t>Vowel Elongation and Repetition</t>
+  </si>
+  <si>
+    <t>Evidence: "niiiyamai" Rationale: Vowel 'i' is repeated to show excitement.</t>
   </si>
   <si>
     <t>Neg_0040</t>
   </si>
   <si>
-    <t>meetingekee link eka ewanna.</t>
-  </si>
-  <si>
-    <t>meetingඑකේ link එක එවන්න.</t>
-  </si>
-  <si>
-    <t>meetingඑකෙ link එක එwඅන්න.</t>
-  </si>
-  <si>
-    <t>Evidence: "meetingekee" Rationale: English word meeting attached to suffix</t>
+    <t>suuupiri wadak.</t>
+  </si>
+  <si>
+    <t>සුපිරි වැඩක්.</t>
+  </si>
+  <si>
+    <t>සුඋඋපිරි wඅඩක්.</t>
+  </si>
+  <si>
+    <t>Evidence: "suuupiri" Rationale: Vowel 'u' is repeated for emphasis.</t>
   </si>
   <si>
     <t>Neg_0041</t>
   </si>
   <si>
-    <t>whatsappeken call ekak.</t>
-  </si>
-  <si>
-    <t>whatsappඑකෙන් call එකක්.</t>
-  </si>
-  <si>
-    <t>wහට්සප්එකෙන් call එකක්.</t>
-  </si>
-  <si>
-    <t>Evidence: "whatsappeken" Rationale: App name whatsapp attached to suffix</t>
+    <t>patttta seen eka.</t>
+  </si>
+  <si>
+    <t>පට්ට seen එක.</t>
+  </si>
+  <si>
+    <t>පට්ට්ට්ට seen එක.</t>
+  </si>
+  <si>
+    <t>Consonant Repetition for Emphasis</t>
+  </si>
+  <si>
+    <t>Evidence: "patttta" Rationale: Consonant 't' is repeated for emphasis.</t>
   </si>
   <si>
     <t>Neg_0042</t>
   </si>
   <si>
-    <t>facebookekee photo eka.</t>
-  </si>
-  <si>
-    <t>facebookඑකේ photo එක.</t>
-  </si>
-  <si>
-    <t>fඅcඑබොඔකෙකෙඑ photo එක.</t>
-  </si>
-  <si>
-    <t>Evidence: "facebookekee" Rationale: App name facebook attached to suffix</t>
+    <t>marruuu bhande.</t>
+  </si>
+  <si>
+    <t>මරු භාණ්ඩේ.</t>
+  </si>
+  <si>
+    <t>මර්‍ර්‍රූඋඋ bහන්ඩෙ.</t>
+  </si>
+  <si>
+    <t>Evidence: "marruuu" Rationale: Consonant 'r' is repeated heavily.</t>
   </si>
   <si>
     <t>Neg_0043</t>
   </si>
   <si>
-    <t>kohomada???!!!</t>
-  </si>
-  <si>
-    <t>කොහොමද???!!!</t>
-  </si>
-  <si>
-    <t>කොහොමඩ???!!!</t>
-  </si>
-  <si>
-    <t>Evidence: "???!!!" Rationale: Heavy consecutive punctuation</t>
+    <t>take care machan.</t>
+  </si>
+  <si>
+    <t>take care මචන්.</t>
+  </si>
+  <si>
+    <t>ටකෙ චරෙ mඅච්න්.</t>
+  </si>
+  <si>
+    <t>Multi-Word English Phrases in Singlish</t>
+  </si>
+  <si>
+    <t>Evidence: "take care" Rationale: A two-word English phrase embedded in the sentence.</t>
   </si>
   <si>
     <t>Neg_0044</t>
   </si>
   <si>
-    <t>yamu!!..</t>
-  </si>
-  <si>
-    <t>යමු!!..</t>
-  </si>
-  <si>
-    <t>Evidence: "!!.." Rationale: Mixed consecutive punctuation marks</t>
+    <t>good morning yaluwane.</t>
+  </si>
+  <si>
+    <t>good morning යාලුවනේ.</t>
+  </si>
+  <si>
+    <t>ගොඔඩ් මොර්නින්ග් යාලුwඅනෙ.</t>
+  </si>
+  <si>
+    <t>Evidence: "good morning" Rationale: A common English greeting phrase used directly.</t>
   </si>
   <si>
     <t>Neg_0045</t>
   </si>
   <si>
-    <t>eka nam siraa...</t>
-  </si>
-  <si>
-    <t>ඒක නම් සිරා...</t>
-  </si>
-  <si>
-    <t>එක නම් සිර...</t>
-  </si>
-  <si>
-    <t>Evidence: "siraa..." Rationale: Trailing punctuation at end of word</t>
+    <t>50% discount thiyenawa.</t>
+  </si>
+  <si>
+    <t>50% discount තියෙනවා.</t>
+  </si>
+  <si>
+    <t>50% දිස්චොඋන්ට් තියෙනwඅ.</t>
+  </si>
+  <si>
+    <t>Inputs with Percentages and Math Symbols</t>
+  </si>
+  <si>
+    <t>Evidence: "50%" Rationale: Contains a percentage symbol.</t>
   </si>
   <si>
     <t>Neg_0046</t>
   </si>
   <si>
-    <t>thiyennaaaaa</t>
-  </si>
-  <si>
-    <t>තියෙන්නාආආආආ</t>
-  </si>
-  <si>
-    <t>Evidence: "thiyennaaaaa" Rationale: Vowel elongated through excessive repetition</t>
+    <t>10+20 kiyada?</t>
+  </si>
+  <si>
+    <t>10+20 කීයද?</t>
+  </si>
+  <si>
+    <t>10+20 කියඩ?</t>
+  </si>
+  <si>
+    <t>Evidence: "10+20" Rationale: Contains a mathematical addition symbol.</t>
   </si>
   <si>
     <t>Neg_0047</t>
   </si>
   <si>
-    <t>ooooone mata.</t>
-  </si>
-  <si>
-    <t>ඕඕඕඕනේ මට.</t>
-  </si>
-  <si>
-    <t>oඔඔඔනෙ මට.</t>
-  </si>
-  <si>
-    <t>Evidence: "ooooone" Rationale: Starting vowel repeated excessively</t>
+    <t>BoHoMa IsThUThI.</t>
+  </si>
+  <si>
+    <t>බොහොම ස්තුතියි.</t>
+  </si>
+  <si>
+    <t>BඔHඔMඅ Iස්ThඋThI.</t>
+  </si>
+  <si>
+    <t>Inputs with Mixed Capitalization</t>
+  </si>
+  <si>
+    <t>Evidence: "BoHoMa IsThUThI" Rationale: Alternating capital and lowercase letters.</t>
   </si>
   <si>
     <t>Neg_0048</t>
   </si>
   <si>
-    <t>plzz udaw karanna.</t>
-  </si>
-  <si>
-    <t>please උදව් කරන්න.</t>
-  </si>
-  <si>
-    <t>plzz උඩව් කරන්න.</t>
-  </si>
-  <si>
-    <t>Multi-Word English Phrases in Singlish</t>
-  </si>
-  <si>
-    <t>Evidence: "plzz udaw karanna." Rationale: English slang phrasing mixed with Sinhala</t>
+    <t>MeKa MaGe.</t>
+  </si>
+  <si>
+    <t>මේක මගේ.</t>
+  </si>
+  <si>
+    <t>MඑKඅ MඅGඑ.</t>
+  </si>
+  <si>
+    <t>Evidence: "MeKa MaGe" Rationale: Unconventional camel-case style capitalization.</t>
   </si>
   <si>
     <t>Neg_0049</t>
   </si>
   <si>
-    <t>thx machan!</t>
-  </si>
-  <si>
-    <t>thanks මචන්!</t>
-  </si>
-  <si>
-    <t>thx මචන්!</t>
-  </si>
-  <si>
-    <t>Evidence: "thx machan!" Rationale: English slang mixed with Sinhala</t>
+    <t>patta kathawa eka 😂</t>
+  </si>
+  <si>
+    <t>පට්ට කතාව ඒක 😂</t>
+  </si>
+  <si>
+    <t>පට්ට කතාව එක ??</t>
+  </si>
+  <si>
+    <t>Inputs Containing Emojis</t>
+  </si>
+  <si>
+    <t>Evidence: "😂" Rationale: Sentence ends with a laughing emoji.</t>
   </si>
   <si>
     <t>Neg_0050</t>
   </si>
   <si>
-    <t>req eka accept karanna.</t>
-  </si>
-  <si>
-    <t>request එක accept කරන්න.</t>
-  </si>
-  <si>
-    <t>req එක aච්චෙප්ට් කරන්න.</t>
-  </si>
-  <si>
-    <t>Evidence: "req eka accept karanna." Rationale: Multiple English words within Singlish</t>
+    <t>mama ada gihin ennam 🚶‍♂️</t>
+  </si>
+  <si>
+    <t>මම අද ගිහින් එන්නම් 🚶‍♂️</t>
+  </si>
+  <si>
+    <t>මම අද ගිහින් එන්නම් 🚶?♂️</t>
+  </si>
+  <si>
+    <t>Evidence: "🚶‍♂️" Rationale: Includes a composite emoji symbol.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -848,6 +910,13 @@
     <font>
       <sz val="8.5"/>
       <color rgb="FF1F1F1F"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="8.5"/>
+      <color theme="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -884,20 +953,24 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1176,19 +1249,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr defaultRowHeight="49.95" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.88671875" customWidth="1"/>
     <col min="3" max="3" width="22.109375" customWidth="1"/>
     <col min="4" max="4" width="25.33203125" customWidth="1"/>
     <col min="5" max="5" width="22.5546875" customWidth="1"/>
-    <col min="7" max="7" width="32" customWidth="1"/>
-    <col min="8" max="8" width="38.88671875" customWidth="1"/>
+    <col min="7" max="7" width="28.77734375" customWidth="1"/>
+    <col min="8" max="8" width="43.77734375" customWidth="1"/>
     <col min="9" max="10" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="49.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1214,7 +1287,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -1240,7 +1313,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>16</v>
       </c>
@@ -1260,41 +1333,39 @@
         <v>13</v>
       </c>
       <c r="G3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="2" t="s">
+    </row>
+    <row r="4" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="J3" s="3"/>
-    </row>
-    <row r="4" spans="1:10" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="B4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>20</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="J4" s="3"/>
-    </row>
-    <row r="5" spans="1:10" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>27</v>
       </c>
@@ -1314,383 +1385,382 @@
         <v>13</v>
       </c>
       <c r="G5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H5" s="2" t="s">
+    </row>
+    <row r="6" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="J5" s="3"/>
-    </row>
-    <row r="6" spans="1:10" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="B6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>38</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" s="2" t="s">
+    </row>
+    <row r="8" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="B8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="H8" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" s="2" t="s">
+    </row>
+    <row r="9" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="B9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="F9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E9" s="2" t="s">
+    </row>
+    <row r="10" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" s="2" t="s">
+      <c r="B10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="H10" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E10" s="2" t="s">
+    </row>
+    <row r="11" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H10" s="2" t="s">
+      <c r="B11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="F11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="E11" s="2" t="s">
+    </row>
+    <row r="12" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11" s="2" t="s">
+      <c r="B12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="F12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="H12" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="E12" s="2" t="s">
+    </row>
+    <row r="13" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" s="2" t="s">
+      <c r="B13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="H12" s="2" t="s">
+      <c r="D13" s="2" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D13" s="2" t="s">
+    </row>
+    <row r="14" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="B14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H13" s="2" t="s">
+      <c r="D14" s="2" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="H14" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="E14" s="2" t="s">
+    </row>
+    <row r="15" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="H14" s="2" t="s">
+      <c r="B15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+      <c r="D15" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="2" t="s">
+      <c r="E15" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="F15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H15" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="E15" s="2" t="s">
+    </row>
+    <row r="16" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="F15" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H15" s="2" t="s">
+      <c r="B16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
+      <c r="D16" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="H16" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="2" t="s">
+      <c r="E17" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="F17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H17" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="2" t="s">
+      <c r="E18" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="H18" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="E19" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="H19" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>110</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>9</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>111</v>
@@ -1699,826 +1769,830 @@
         <v>112</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>72</v>
+        <v>114</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="H21" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>121</v>
+        <v>110</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>123</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>39</v>
+        <v>110</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>14</v>
-      </c>
       <c r="H23" s="2" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>9</v>
+        <v>110</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>14</v>
+        <v>136</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>9</v>
+        <v>110</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D25" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G25" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="H25" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>66</v>
+        <v>147</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="E27" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G27" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="F27" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>14</v>
-      </c>
       <c r="H27" s="2" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>66</v>
+        <v>158</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>72</v>
+        <v>158</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>72</v>
+        <v>169</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>72</v>
+        <v>169</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>43</v>
+        <v>180</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>72</v>
+        <v>180</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>9</v>
+        <v>110</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>14</v>
+        <v>191</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>9</v>
+        <v>110</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>49</v>
+        <v>191</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>72</v>
+        <v>202</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>20</v>
+        <v>213</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>49</v>
+        <v>224</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>49</v>
+        <v>224</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>31</v>
+        <v>235</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>31</v>
+        <v>235</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>55</v>
+        <v>246</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>9</v>
+        <v>110</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>55</v>
+        <v>246</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>237</v>
+        <v>252</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>238</v>
+        <v>253</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>239</v>
+        <v>254</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>55</v>
+        <v>257</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>242</v>
+        <v>258</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>243</v>
+        <v>259</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>245</v>
+        <v>261</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>245</v>
+        <v>262</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>72</v>
+        <v>257</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>249</v>
+        <v>266</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>72</v>
+        <v>268</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>251</v>
+        <v>269</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>255</v>
+        <v>273</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>259</v>
+        <v>276</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>260</v>
+        <v>277</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>261</v>
+        <v>278</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>262</v>
+        <v>280</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>263</v>
+        <v>281</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>264</v>
+        <v>282</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>265</v>
+        <v>283</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>266</v>
+        <v>284</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>267</v>
+        <v>285</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C22" r:id="rId1" display="https://www.google.com/search?q=https://lms.sliit.lk" xr:uid="{F420E629-0462-4F6B-B5BE-564B010B0E63}"/>
+    <hyperlink ref="D22" r:id="rId2" display="https://www.google.com/search?q=https://lms.sliit.lk" xr:uid="{F26D9ACB-9AAE-4D1F-968E-3C1E9D0955FE}"/>
+    <hyperlink ref="H22" r:id="rId3" display="https://www.google.com/search?q=https://lms.sliit.lk" xr:uid="{A3DF3CC1-FB35-4F7D-9190-4D9B5F8CFA21}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Assignment 1 - Test cases.xlsx
+++ b/Assignment 1 - Test cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\ITPM_Assignment_1_Final\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC44F482-896C-41AD-9165-A6FDAA5D835F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83C6C70C-D3BD-4B0E-A412-A3877CCA73FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="722" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -139,18 +139,6 @@
     <t>Neg_0006</t>
   </si>
   <si>
-    <t>tiktok eka blnna.</t>
-  </si>
-  <si>
-    <t>TikTok එක බලන්න.</t>
-  </si>
-  <si>
-    <t>ටික්ටොක් එක bල්න්න.</t>
-  </si>
-  <si>
-    <t>Evidence: "tiktok" Rationale: App name TikTok is used.</t>
-  </si>
-  <si>
     <t>Neg_0007</t>
   </si>
   <si>
@@ -355,21 +343,9 @@
     <t>M</t>
   </si>
   <si>
-    <t>rs. 150.50 k dhenna.</t>
-  </si>
-  <si>
-    <t>රුපියල් 150.50 ක් දෙන්න.</t>
-  </si>
-  <si>
-    <t>ර්ස්. 150.50 k ධෙන්න.</t>
-  </si>
-  <si>
     <t>Inputs with Currency and Pricing</t>
   </si>
   <si>
-    <t>Evidence: "rs. 150.50" Rationale: Uses currency abbreviation and decimal pricing.</t>
-  </si>
-  <si>
     <t>Neg_0020</t>
   </si>
   <si>
@@ -472,18 +448,6 @@
     <t>Neg_0026</t>
   </si>
   <si>
-    <t>15-Aug-2024 dhi gamu.</t>
-  </si>
-  <si>
-    <t>15-Aug-2024 දී ගමු.</t>
-  </si>
-  <si>
-    <t>15-අඋග්-2024 ධි ගමු.</t>
-  </si>
-  <si>
-    <t>Evidence: "15-Aug-2024" Rationale: Uses date format with month abbreviation.</t>
-  </si>
-  <si>
     <t>Neg_0027</t>
   </si>
   <si>
@@ -878,6 +842,42 @@
   </si>
   <si>
     <t>Evidence: "🚶‍♂️" Rationale: Includes a composite emoji symbol.</t>
+  </si>
+  <si>
+    <t>telegram eka blnna.</t>
+  </si>
+  <si>
+    <t>telegram එක බලන්න.</t>
+  </si>
+  <si>
+    <t>ටෙලිග්රම් එක bල්න්න.</t>
+  </si>
+  <si>
+    <t>Evidence: "telegram" Rationale: App name telegram is used.</t>
+  </si>
+  <si>
+    <t>rs. 890.50 k dhenna.</t>
+  </si>
+  <si>
+    <t>රුපියල් 890.50 ක් දෙන්න.</t>
+  </si>
+  <si>
+    <t>ර්ස්. 890.50 k ධෙන්න.</t>
+  </si>
+  <si>
+    <t>Evidence: "rs. 890.50" Rationale: Uses currency abbreviation and decimal pricing.</t>
+  </si>
+  <si>
+    <t>15-Aug-2026 dhi gamu.</t>
+  </si>
+  <si>
+    <t>15-Aug-2026 දී ගමු.</t>
+  </si>
+  <si>
+    <t>15-අඋග්-2026 ධි ගමු.</t>
+  </si>
+  <si>
+    <t>Evidence: "15-Aug-2026" Rationale: Uses date format with month abbreviation.</t>
   </si>
 </sst>
 </file>
@@ -1425,13 +1425,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>39</v>
+        <v>274</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>40</v>
+        <v>275</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>41</v>
+        <v>276</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>13</v>
@@ -1440,1151 +1440,1151 @@
         <v>36</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>42</v>
+        <v>277</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="H8" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="2" t="s">
+      <c r="H10" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="H12" s="2" t="s">
         <v>66</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>71</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="2" t="s">
+      <c r="H14" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H15" s="2" t="s">
         <v>82</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="2" t="s">
+      <c r="H16" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H17" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="2" t="s">
+      <c r="H18" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H19" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>111</v>
+        <v>278</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>112</v>
+        <v>279</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>113</v>
+        <v>280</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>115</v>
+        <v>281</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>118</v>
-      </c>
       <c r="E21" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>150</v>
+        <v>282</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>151</v>
+        <v>283</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>152</v>
+        <v>284</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>153</v>
+        <v>285</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
     </row>
   </sheetData>
